--- a/Teorie/2.IT/APP/vyuka.xlsx
+++ b/Teorie/2.IT/APP/vyuka.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\it-martinsramek\Downloads\SCMSD-IT-Martin-Sramek\Teorie\2.IT\APP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scmsd-my.sharepoint.com/personal/it-martinsramek_stredniskola_com/Documents/Plocha/SCMSD-IT-Martin-Sramek/Teorie/2.IT/APP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF7D94A-D570-4815-AB57-C20EE0AF4DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{ADF7D94A-D570-4815-AB57-C20EE0AF4DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4845B5F4-24F4-4026-9625-D3EA77E71A06}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C7735200-00CF-4C48-B66D-CD3C1184F066}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7735200-00CF-4C48-B66D-CD3C1184F066}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -276,6 +276,56 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>149305</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>162367</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Obrázek 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C37E60B-73A0-8B57-CAA1-F04EDCBB0B8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2266950" y="1343025"/>
+          <a:ext cx="8245555" cy="5105842"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/Teorie/2.IT/APP/vyuka.xlsx
+++ b/Teorie/2.IT/APP/vyuka.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scmsd-my.sharepoint.com/personal/it-martinsramek_stredniskola_com/Documents/Plocha/SCMSD-IT-Martin-Sramek/Teorie/2.IT/APP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{ADF7D94A-D570-4815-AB57-C20EE0AF4DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4845B5F4-24F4-4026-9625-D3EA77E71A06}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{ADF7D94A-D570-4815-AB57-C20EE0AF4DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70008769-0537-42AA-8939-95A00EBF0F14}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7735200-00CF-4C48-B66D-CD3C1184F066}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C7735200-00CF-4C48-B66D-CD3C1184F066}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
-    <sheet name="rady" sheetId="2" r:id="rId2"/>
+    <sheet name="vzorce" sheetId="3" r:id="rId2"/>
+    <sheet name="rady" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
   <si>
     <t>výuka aplikacniho programu Ms exel</t>
   </si>
@@ -100,6 +101,9 @@
   </si>
   <si>
     <t>Ne</t>
+  </si>
+  <si>
+    <t>Vzorce</t>
   </si>
 </sst>
 </file>
@@ -329,6 +333,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -663,6 +671,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975FF9FE-9C31-4DF2-83A5-CD4E001C8C28}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8890AB2B-EA0E-4FDF-A695-B189D03F432F}">
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
